--- a/sheets/personal-finance/refi-or-paydown/refi-or-paydown.xlsx
+++ b/sheets/personal-finance/refi-or-paydown/refi-or-paydown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\personal-finance\refi-or-paydown\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D508C89D-1113-4847-9169-BE6EC10BD1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405144BB-5AF9-4543-899E-D4CC78BF9E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>Current Home Value</t>
   </si>
   <si>
-    <t>Compare here</t>
-  </si>
-  <si>
     <t>Current Mortgage Balance</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>Invest</t>
+  </si>
+  <si>
+    <t>Comparison</t>
   </si>
 </sst>
 </file>
@@ -191,7 +191,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,8 +218,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF4472C4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,6 +258,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F2E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -274,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -303,20 +323,41 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -353,11 +394,19 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="1400"/>
-              <a:t>Net worth lines</a:t>
+              <a:t>Net worth </a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.38129547675153747"/>
+          <c:y val="3.0010718113612004E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -370,7 +419,7 @@
           <c:x val="7.0555555555555552E-2"/>
           <c:y val="0.11591269841269841"/>
           <c:w val="0.7365225970841236"/>
-          <c:h val="0.82865079365079364"/>
+          <c:h val="0.75576777983137955"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -732,10 +781,10 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="100"/>
@@ -752,7 +801,17 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -760,10 +819,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1100" b="0"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1100" b="0"/>
                   <a:t>Net Worth Proxy</a:t>
                 </a:r>
               </a:p>
@@ -1083,7 +1142,17 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1133,10 +1202,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>34529</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>153589</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5219700" cy="2962275"/>
     <xdr:graphicFrame macro="">
@@ -1164,10 +1233,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4748625" cy="2933700"/>
     <xdr:graphicFrame macro="">
@@ -1487,6 +1556,7 @@
     <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1498,61 +1568,61 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="4" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>338000</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2" s="13">
         <f>B5</f>
         <v>2313.8086120901867</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="7">
         <v>6.9500000000000006E-2</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="6">
+        <v>4</v>
+      </c>
+      <c r="E3" s="13">
         <f>B14</f>
         <v>2038.2459275894316</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="8">
         <v>27</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="6">
+        <v>6</v>
+      </c>
+      <c r="E4" s="13">
         <f>B15</f>
         <v>275.56268450075504</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="9">
         <f>PMT(B3/12,B4*12,-B2)</f>
@@ -1560,16 +1630,16 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="10" t="str">
+        <v>8</v>
+      </c>
+      <c r="E5" s="14" t="str">
         <f ca="1">'Break-Even &amp; Summary'!B13</f>
         <v>&gt;10 years</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="7">
         <v>5.8500000000000003E-2</v>
@@ -1580,7 +1650,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -1591,7 +1661,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3">
         <v>7500</v>
@@ -1602,7 +1672,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3">
         <v>300</v>
@@ -1613,9 +1683,9 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="11">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C10" s="1"/>
@@ -1624,9 +1694,9 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="11">
+        <v>14</v>
+      </c>
+      <c r="B11" s="10">
         <v>0.03</v>
       </c>
       <c r="C11" s="1"/>
@@ -1635,7 +1705,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="8">
         <v>10</v>
@@ -1646,7 +1716,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="9">
         <f>B2+B8</f>
@@ -1658,7 +1728,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="9">
         <f>PMT(B6/12,B7*12,-B13)</f>
@@ -1670,7 +1740,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="9">
         <f>B5-B14</f>
@@ -1691,43 +1761,40 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>0</v>
       </c>
       <c r="B2" s="9">
@@ -1760,7 +1827,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
       <c r="B3" s="9">
@@ -1793,7 +1860,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
       <c r="B4" s="9">
@@ -1826,7 +1893,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
       <c r="B5" s="9">
@@ -1859,7 +1926,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
       <c r="B6" s="9">
@@ -1892,7 +1959,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
       <c r="B7" s="9">
@@ -1925,7 +1992,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
       <c r="B8" s="9">
@@ -1958,7 +2025,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
       <c r="B9" s="9">
@@ -1991,7 +2058,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
       <c r="B10" s="9">
@@ -2024,7 +2091,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
       <c r="B11" s="9">
@@ -2057,7 +2124,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
       <c r="B12" s="9">
@@ -2090,7 +2157,40 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H2:H12">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6BB83928-A369-4873-A900-AE2835E81860}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6BB83928-A369-4873-A900-AE2835E81860}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H2:H12</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2102,47 +2202,49 @@
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="21" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>0</v>
       </c>
       <c r="B2" s="9">
@@ -2153,7 +2255,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A2</f>
         <v>515000</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="20">
         <f t="shared" ref="D2:D12" si="0">C2-B2</f>
         <v>177000</v>
       </c>
@@ -2174,16 +2276,16 @@
         <v>177000</v>
       </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="13" t="str">
+      <c r="J2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="17" t="str">
         <f ca="1">IFERROR(_xludf.MINIFS(A2:A12,B2:B12,"&lt;=0"),"&gt;10 years")</f>
         <v>&gt;10 years</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
       <c r="B3" s="9">
@@ -2194,7 +2296,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A3</f>
         <v>530450</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="20">
         <f t="shared" si="0"/>
         <v>200580.45179871749</v>
       </c>
@@ -2219,7 +2321,7 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
       <c r="B4" s="9">
@@ -2230,7 +2332,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A4</f>
         <v>546363.5</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="20">
         <f t="shared" si="0"/>
         <v>225207.82178184588</v>
       </c>
@@ -2255,7 +2357,7 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
       <c r="B5" s="9">
@@ -2266,7 +2368,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A5</f>
         <v>562754.40500000003</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="20">
         <f t="shared" si="0"/>
         <v>250937.87938525289</v>
       </c>
@@ -2291,7 +2393,7 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
       <c r="B6" s="9">
@@ -2302,7 +2404,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A6</f>
         <v>579637.03714999999</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="20">
         <f t="shared" si="0"/>
         <v>277829.81526810583</v>
       </c>
@@ -2327,7 +2429,7 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
       <c r="B7" s="9">
@@ -2338,7 +2440,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A7</f>
         <v>597026.14826449996</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="20">
         <f t="shared" si="0"/>
         <v>305946.46939116064</v>
       </c>
@@ -2363,7 +2465,7 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
       <c r="B8" s="9">
@@ -2374,7 +2476,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A8</f>
         <v>614936.93271243491</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>335354.57493873127</v>
       </c>
@@ -2399,7 +2501,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
       <c r="B9" s="9">
@@ -2410,7 +2512,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A9</f>
         <v>633385.040693808</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="20">
         <f t="shared" si="0"/>
         <v>366125.0192055626</v>
       </c>
@@ -2435,7 +2537,7 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
       <c r="B10" s="9">
@@ -2446,7 +2548,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A10</f>
         <v>652386.59191462223</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="20">
         <f t="shared" si="0"/>
         <v>398333.12264980999</v>
       </c>
@@ -2471,7 +2573,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
       <c r="B11" s="9">
@@ -2482,7 +2584,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A11</f>
         <v>671958.18967206089</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="20">
         <f t="shared" si="0"/>
         <v>432058.9373990458</v>
       </c>
@@ -2507,7 +2609,7 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
       <c r="B12" s="9">
@@ -2518,7 +2620,7 @@
         <f>Inputs!$B$1*(1+Inputs!$B$11)^A12</f>
         <v>692116.93536222272</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="20">
         <f t="shared" si="0"/>
         <v>467387.56658805115</v>
       </c>
@@ -2564,32 +2666,32 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="E1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>0</v>
       </c>
       <c r="B2" s="9">
@@ -2622,7 +2724,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
       <c r="B3" s="9">
@@ -2655,7 +2757,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
       <c r="B4" s="9">
@@ -2688,7 +2790,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
       <c r="B5" s="9">
@@ -2721,7 +2823,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
       <c r="B6" s="9">
@@ -2754,7 +2856,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
       <c r="B7" s="9">
@@ -2787,7 +2889,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
       <c r="B8" s="9">
@@ -2820,7 +2922,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
       <c r="B9" s="9">
@@ -2853,7 +2955,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
       <c r="B10" s="9">
@@ -2886,7 +2988,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
       <c r="B11" s="9">
@@ -2919,7 +3021,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
       <c r="B12" s="9">
@@ -2970,7 +3072,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="6">
         <f>Inputs!B5</f>
@@ -2989,7 +3091,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6">
         <f>Inputs!B14</f>
@@ -3008,7 +3110,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="6">
         <f>Inputs!B5+Inputs!B9</f>
@@ -3027,7 +3129,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6">
         <f>Inputs!B9</f>
@@ -3060,7 +3162,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="6">
         <f>'Refi Case'!H3</f>
@@ -3079,7 +3181,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="6">
         <f>'Extra Paydown Case'!H3</f>
@@ -3098,7 +3200,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="6">
         <f>'Invest Case'!H3</f>
@@ -3117,7 +3219,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="6">
         <f>'Refi Case'!H12</f>
@@ -3136,7 +3238,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6">
         <f>'Extra Paydown Case'!H12</f>
@@ -3155,7 +3257,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6">
         <f>'Invest Case'!H12</f>
@@ -3188,9 +3290,9 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="14" t="str">
+        <v>39</v>
+      </c>
+      <c r="B13" s="12" t="str">
         <f ca="1">IFERROR(_xludf.MINIFS(A19:A28,B19:B28,"&gt;=0"),"&gt;10 years")</f>
         <v>&gt;10 years</v>
       </c>
@@ -3263,33 +3365,33 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="A19" s="11">
         <v>1</v>
       </c>
       <c r="B19" s="9">
@@ -3305,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="12">
+      <c r="F19" s="11">
         <v>0</v>
       </c>
       <c r="G19" s="9">
@@ -3322,7 +3424,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+      <c r="A20" s="11">
         <v>2</v>
       </c>
       <c r="B20" s="9">
@@ -3338,7 +3440,7 @@
         <v>3717.7755868921313</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <v>1</v>
       </c>
       <c r="G20" s="9">
@@ -3355,7 +3457,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="A21" s="11">
         <v>3</v>
       </c>
       <c r="B21" s="9">
@@ -3371,7 +3473,7 @@
         <v>7704.3094715660382</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="12">
+      <c r="F21" s="11">
         <v>2</v>
       </c>
       <c r="G21" s="9">
@@ -3388,7 +3490,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="A22" s="11">
         <v>4</v>
       </c>
       <c r="B22" s="9">
@@ -3404,7 +3506,7 @@
         <v>11979.030213099144</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="12">
+      <c r="F22" s="11">
         <v>3</v>
       </c>
       <c r="G22" s="9">
@@ -3421,7 +3523,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+      <c r="A23" s="11">
         <v>5</v>
       </c>
       <c r="B23" s="9">
@@ -3437,7 +3539,7 @@
         <v>16562.770862675501</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="12">
+      <c r="F23" s="11">
         <v>4</v>
       </c>
       <c r="G23" s="9">
@@ -3454,7 +3556,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+      <c r="A24" s="11">
         <v>6</v>
       </c>
       <c r="B24" s="9">
@@ -3470,7 +3572,7 @@
         <v>21477.870494433759</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <v>5</v>
       </c>
       <c r="G24" s="9">
@@ -3487,7 +3589,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+      <c r="A25" s="11">
         <v>7</v>
       </c>
       <c r="B25" s="9">
@@ -3503,7 +3605,7 @@
         <v>26748.283075988275</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="12">
+      <c r="F25" s="11">
         <v>6</v>
       </c>
       <c r="G25" s="9">
@@ -3520,7 +3622,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="A26" s="11">
         <v>8</v>
       </c>
       <c r="B26" s="9">
@@ -3536,7 +3638,7 @@
         <v>32399.694209209079</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="12">
+      <c r="F26" s="11">
         <v>7</v>
       </c>
       <c r="G26" s="9">
@@ -3553,7 +3655,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+      <c r="A27" s="11">
         <v>9</v>
       </c>
       <c r="B27" s="9">
@@ -3569,7 +3671,7 @@
         <v>38459.646310202254</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="12">
+      <c r="F27" s="11">
         <v>8</v>
       </c>
       <c r="G27" s="9">
@@ -3586,7 +3688,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+      <c r="A28" s="11">
         <v>10</v>
       </c>
       <c r="B28" s="9">
@@ -3602,7 +3704,7 @@
         <v>44957.672838561135</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="12">
+      <c r="F28" s="11">
         <v>9</v>
       </c>
       <c r="G28" s="9">
@@ -3624,7 +3726,7 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="12">
+      <c r="F29" s="11">
         <v>10</v>
       </c>
       <c r="G29" s="9">
